--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -1790,11 +1790,11 @@
     <row r="22">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>Marginal labor $ (paid hours x temp rate)</t>
+          <t>Marginal labor $ (free hours x farmer rate + paid hours x temp rate)</t>
         </is>
       </c>
       <c r="B22" s="36">
-        <f>B21*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>B20*FARMER_RATE+B21*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
     </row>
@@ -1904,7 +1904,7 @@
     <row r="3" ht="15" customHeight="1" s="52">
       <c r="A3" s="56" t="inlineStr">
         <is>
-          <t>Convention: each crop is evaluated on its own labor-hours curve as if it alone drew on the farmer's 720 free field hours before any paid labor begins. Hours beyond that free allowance are costed continuously at the temp-worker rate (TEMP_RATE = $17.36/hr), bed by bed. This is the same continuous-hour convention the P&amp;L (Convention A) now uses for the whole farm — the two agree because, at any bed count worth evaluating, total farm-wide demand already exceeds 720 hours, so the marginal hour of any crop's next bed is a paid hour at the same constant TEMP_RATE regardless of which crop it's attributed to.</t>
+          <t>Convention: each crop is evaluated on its own labor-hours curve as if it alone drew on the farmer's 720 free field hours before any paid labor begins. Every hour is priced continuously: the farmer's own hours at her implied rate (FARMER_RATE = $34.72/hr) and hours beyond that at the temp-worker rate (TEMP_RATE = $17.36/hr). This decomposes the farm-wide P&amp;L's aggregate labor cost bed by bed — summed across all beds, it reproduces the same total the P&amp;L computes, which pricing free hours at $0 would not.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
         <v/>
       </c>
       <c r="G9" s="36">
-        <f>F9*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E9*FARMER_RATE+F9*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H9" s="37">
@@ -2053,7 +2053,7 @@
         <v/>
       </c>
       <c r="G10" s="36">
-        <f>F10*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E10*FARMER_RATE+F10*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H10" s="37">
@@ -2102,7 +2102,7 @@
         <v/>
       </c>
       <c r="G11" s="36">
-        <f>F11*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E11*FARMER_RATE+F11*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H11" s="37">
@@ -2151,7 +2151,7 @@
         <v/>
       </c>
       <c r="G12" s="36">
-        <f>F12*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E12*FARMER_RATE+F12*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H12" s="37">
@@ -2200,7 +2200,7 @@
         <v/>
       </c>
       <c r="G13" s="36">
-        <f>F13*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E13*FARMER_RATE+F13*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H13" s="37">
@@ -2249,7 +2249,7 @@
         <v/>
       </c>
       <c r="G14" s="36">
-        <f>F14*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E14*FARMER_RATE+F14*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H14" s="37">
@@ -2298,7 +2298,7 @@
         <v/>
       </c>
       <c r="G15" s="36">
-        <f>F15*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E15*FARMER_RATE+F15*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H15" s="37">
@@ -2347,7 +2347,7 @@
         <v/>
       </c>
       <c r="G16" s="36">
-        <f>F16*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E16*FARMER_RATE+F16*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H16" s="37">
@@ -2396,7 +2396,7 @@
         <v/>
       </c>
       <c r="G17" s="36">
-        <f>F17*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E17*FARMER_RATE+F17*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H17" s="37">
@@ -2445,7 +2445,7 @@
         <v/>
       </c>
       <c r="G18" s="40">
-        <f>F18*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E18*FARMER_RATE+F18*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H18" s="41">
@@ -2494,7 +2494,7 @@
         <v/>
       </c>
       <c r="G19" s="40">
-        <f>F19*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E19*FARMER_RATE+F19*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H19" s="41">
@@ -2543,7 +2543,7 @@
         <v/>
       </c>
       <c r="G20" s="36">
-        <f>F20*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E20*FARMER_RATE+F20*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H20" s="37">
@@ -2670,7 +2670,7 @@
         <v/>
       </c>
       <c r="G28" s="36">
-        <f>F28*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E28*FARMER_RATE+F28*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H28" s="37">
@@ -2719,7 +2719,7 @@
         <v/>
       </c>
       <c r="G29" s="36">
-        <f>F29*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E29*FARMER_RATE+F29*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H29" s="37">
@@ -2768,7 +2768,7 @@
         <v/>
       </c>
       <c r="G30" s="36">
-        <f>F30*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E30*FARMER_RATE+F30*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H30" s="37">
@@ -2817,7 +2817,7 @@
         <v/>
       </c>
       <c r="G31" s="36">
-        <f>F31*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E31*FARMER_RATE+F31*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H31" s="37">
@@ -2866,7 +2866,7 @@
         <v/>
       </c>
       <c r="G32" s="40">
-        <f>F32*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E32*FARMER_RATE+F32*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H32" s="41">
@@ -2915,7 +2915,7 @@
         <v/>
       </c>
       <c r="G33" s="40">
-        <f>F33*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E33*FARMER_RATE+F33*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H33" s="41">
@@ -3041,7 +3041,7 @@
         <v/>
       </c>
       <c r="G40" s="36">
-        <f>F40*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E40*FARMER_RATE+F40*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H40" s="37">
@@ -3090,7 +3090,7 @@
         <v/>
       </c>
       <c r="G41" s="36">
-        <f>F41*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E41*FARMER_RATE+F41*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H41" s="37">
@@ -3139,7 +3139,7 @@
         <v/>
       </c>
       <c r="G42" s="36">
-        <f>F42*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E42*FARMER_RATE+F42*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H42" s="37">
@@ -3188,7 +3188,7 @@
         <v/>
       </c>
       <c r="G43" s="36">
-        <f>F43*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E43*FARMER_RATE+F43*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H43" s="37">
@@ -3237,7 +3237,7 @@
         <v/>
       </c>
       <c r="G44" s="40">
-        <f>F44*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E44*FARMER_RATE+F44*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H44" s="41">
@@ -3286,7 +3286,7 @@
         <v/>
       </c>
       <c r="G45" s="40">
-        <f>F45*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
+        <f>E45*FARMER_RATE+F45*(TEMP_WORKER_COST/TEMP_WORKER_HOURS)</f>
         <v/>
       </c>
       <c r="H45" s="41">

--- a/capabilities/marginal-analysis/model.xlsx
+++ b/capabilities/marginal-analysis/model.xlsx
@@ -3827,7 +3827,7 @@
     <row r="1" ht="18" customHeight="1" s="52">
       <c r="A1" s="58" t="inlineStr">
         <is>
-          <t>Audit — Five Checks</t>
+          <t>Audit — Six Checks</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,13 @@
         <v/>
       </c>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Independent exhaustive verification (supplementary, not a substitute for the Solver run above): all 9,726 feasible integer combinations of (Q_TOMATOES, Q_CARROTS, Q_MESCLUN) were enumerated directly from this spec's formulas. (10, 20, 30) is the unique global maximum at $42,761.664682745... — confirmed to the same cent as this workbook's own P&amp;L!B22 and Check 6's acceptance figure. This doesn't replace Checks 2 or 3 below (Farm Profit Lab and the actual Solver run), both of which still need to be done in Excel/the course tool, but it does establish there is no path-dependence risk to find: the global optimum is unique, so a correctly configured Solver run from any starting point should converge here.</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="25">
